--- a/outputs/2026-02-04/valid_sharing_details.xlsx
+++ b/outputs/2026-02-04/valid_sharing_details.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5024333195108</t>
+          <t>5024333195382</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5024333261605</t>
+          <t>5024333195108</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -471,14 +471,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Medina, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5024333262190</t>
+          <t>5024333201724</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -486,59 +486,59 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Medina, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4028159119547</t>
+          <t>5024333261605</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13308650355476</t>
+          <t>5024333262190</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05063662004415</t>
+          <t>5410126106282</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5013635116003</t>
+          <t>5024333205173</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -553,7 +553,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5024333195214</t>
+          <t>5024333208518</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5024333208518</t>
+          <t>5024333198383</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -583,7 +583,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5024333258285</t>
+          <t>5024333195160</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -598,7 +598,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5201080601025</t>
+          <t>5024333208525</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -606,14 +606,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7322542403839</t>
+          <t>5024333208532</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -621,704 +621,704 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5024333195719</t>
+          <t>4028159120031</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>35060941970127</t>
+          <t>5024333195351</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4028159118168</t>
+          <t>5024333195368</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland</t>
+          <t>Brakes, Fresh_Direct, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13052911563765</t>
+          <t>5024333195177</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3700478571688</t>
+          <t>5024333195405</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KFF, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05000159551298</t>
+          <t>5024333205197</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13052911616867</t>
+          <t>5024333218937</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brakes, Classic_Drinks, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5010066108522</t>
+          <t>5024333195429</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13052911616003</t>
+          <t>5024333211068</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brakes, Classic_Drinks, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13700417300888</t>
+          <t>5024333205203</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KFF, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05063662001483</t>
+          <t>5024333195184</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, Menigo, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15000225028904</t>
+          <t>4028159121069</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5000157106902</t>
+          <t>5013635116003</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05063662001575</t>
+          <t>5024333204817</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05063662001582</t>
+          <t>5024333195214</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05063662001599</t>
+          <t>5024333207757</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05063662001605</t>
+          <t>05063662004415</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05063662001612</t>
+          <t>5011766110204</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13052911617079</t>
+          <t>5024333116929</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brakes, Classic_Drinks, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4028159100132</t>
+          <t>5024333208570</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13052911616287</t>
+          <t>5029396122757</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brakes, Classic_Drinks, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Classic_Drinks, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15060281501421</t>
+          <t>5024333253303</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13052911616430</t>
+          <t>5024333195245</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brakes, Classic_Drinks, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13187670992638</t>
+          <t>5024333253440</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13052911616577</t>
+          <t>4028159119066</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Classic_Drinks, Fresh_Direct, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13052911616652</t>
+          <t>5024333207061</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brakes, Classic_Drinks, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4040337562105</t>
+          <t>4028159119400</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>43052911236912</t>
+          <t>4028159119523</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4028159118991</t>
+          <t>4028159119547</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5010102340114</t>
+          <t>5024333207498</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5010228504612</t>
+          <t>5024333167815</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5010228504889</t>
+          <t>4028159119585</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5011766110358</t>
+          <t>4028159119738</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4040337565625</t>
+          <t>5019503046571</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5023139639717</t>
+          <t>5024333255628</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5024333001881</t>
+          <t>5024333258285</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5024333010524</t>
+          <t>5024333260233</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5024333127222</t>
+          <t>13308650355476</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5024333179429</t>
+          <t>5024333260295</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13242278271674</t>
+          <t>5024333249832</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4025500247898</t>
+          <t>4028159119813</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5024333197522</t>
+          <t>5024333005414</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5024333199830</t>
+          <t>5201080601025</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5024333205210</t>
+          <t>5024333208617</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5024333206927</t>
+          <t>7322542403839</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5024333207306</t>
+          <t>8711571089814</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5024333208457</t>
+          <t>5024333207771</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1326,14 +1326,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>15060283762264</t>
+          <t>5024333253341</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1341,14 +1341,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5024333208563</t>
+          <t>5024333253365</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5024333208624</t>
+          <t>5011251034114</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1378,7 +1378,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5024333211761</t>
+          <t>5051788122229</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1393,7 +1393,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5024333241294</t>
+          <t>5024333114888</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1408,7 +1408,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5024333249719</t>
+          <t>5000328554709</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1416,14 +1416,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5024333249870</t>
+          <t>5024333179320</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1438,7 +1438,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5024333253341</t>
+          <t>5024333179337</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1453,7 +1453,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5024333254775</t>
+          <t>5024333252399</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1468,7 +1468,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20044738201692</t>
+          <t>5024333221791</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Menigo, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5024333259442</t>
+          <t>5024333196389</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4028159119714</t>
+          <t>5057624174339</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1506,14 +1506,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_France, Sysco_Northern_Ireland</t>
+          <t>Brakes, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5024333261988</t>
+          <t>5024333179405</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1528,7 +1528,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4028159104581</t>
+          <t>5024333253389</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1536,14 +1536,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5024468000216</t>
+          <t>5024333205210</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5038862004619</t>
+          <t>5024333179412</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1566,14 +1566,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5051788122229</t>
+          <t>5024333179429</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1588,7 +1588,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5060360506135</t>
+          <t>5024333221845</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1596,14 +1596,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5099556014314</t>
+          <t>5024333117513</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1618,7 +1618,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>43052911098596</t>
+          <t>5024333208358</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>19555018507747</t>
+          <t>5024333197522</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1641,14 +1641,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>7613036340427</t>
+          <t>5024333208389</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1663,7 +1663,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8008698042632</t>
+          <t>43052911098596</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1671,14 +1671,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, KFF, Medina</t>
+          <t>Brakes, Sysco_France, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8410066146857</t>
+          <t>5024333231110</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8711118033652</t>
+          <t>5024333198376</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1708,7 +1708,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8711571006095</t>
+          <t>5014213500764</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1716,14 +1716,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8712100901348</t>
+          <t>5024333127215</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8719956498664</t>
+          <t>5024333127222</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1746,14 +1746,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8721201955563</t>
+          <t>5024333127239</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1768,180 +1768,180 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>15060381000305</t>
+          <t>4040337562105</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brakes, KFF, Medina</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>25056654609013</t>
+          <t>4040337565625</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>17311310044524</t>
+          <t>5024333199830</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Menigo, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>18437013100004</t>
+          <t>5000159416962</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Classic_Drinks, Menigo, Sysco_Northern_Ireland</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>17311310046184</t>
+          <t>5024333199892</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Menigo, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>05063662001506</t>
+          <t>5024333208457</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brakes, Menigo, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>05063662001568</t>
+          <t>43052911236912</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Menigo, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17311310046504</t>
+          <t>5024333205807</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Menigo, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>05063662002060</t>
+          <t>5053990107490</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct, KFF</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>25056654609020</t>
+          <t>5000328111797</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>28411640000453</t>
+          <t>5024333208501</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Classic_Drinks, Menigo, Sysco_Northern_Ireland</t>
+          <t>Brakes, KFF, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>47312040017056</t>
+          <t>5024333253327</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Classic_Drinks, Menigo, Sysco_Northern_Ireland</t>
+          <t>Brakes, Medina, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
     </row>
